--- a/12613711.xlsx
+++ b/12613711.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B685BA-2B0C-4E04-BACC-9CB7EABC58D4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09641AB-EE2C-4230-9638-72FDA06F5A61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>College fect prep</t>
   </si>
 </sst>
 </file>
@@ -1805,26 +1808,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B40" s="14">
+        <v>320</v>
+      </c>
+      <c r="C40" s="14">
+        <v>25</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>150</v>
+      </c>
+      <c r="G40" s="14">
+        <v>3</v>
+      </c>
+      <c r="H40" s="14">
+        <v>50</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>665</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>775</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>

--- a/12613711.xlsx
+++ b/12613711.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09641AB-EE2C-4230-9638-72FDA06F5A61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF00704-15CE-49DA-A734-0B0E08B681E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,7 +211,7 @@
     <t>Neutral</t>
   </si>
   <si>
-    <t>College fect prep</t>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1809,36 +1809,34 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="B40" s="14">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="C40" s="14">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D40" s="14">
         <v>120</v>
       </c>
       <c r="E40" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F40" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G40" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H40" s="14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I40" s="15">
-        <f t="shared" si="0"/>
-        <v>665</v>
+        <v>625</v>
       </c>
       <c r="J40" s="15">
-        <f t="shared" si="1"/>
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>60</v>
@@ -1847,33 +1845,53 @@
         <v>60</v>
       </c>
       <c r="M40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B41" s="14">
+        <v>250</v>
+      </c>
+      <c r="C41" s="14">
+        <v>30</v>
+      </c>
+      <c r="D41" s="14">
+        <v>200</v>
+      </c>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14"/>
+      <c r="I41" s="15">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J41" s="15">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M41" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="N40" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+      <c r="N41" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>

--- a/12613711.xlsx
+++ b/12613711.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF00704-15CE-49DA-A734-0B0E08B681E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65992337-025D-4ED3-8F55-C977DA4ED78E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,18 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Mostly Practical</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Mostly Induction</t>
   </si>
 </sst>
 </file>
@@ -1741,7 +1753,9 @@
       <c r="G38" s="14">
         <v>2</v>
       </c>
-      <c r="H38" s="14"/>
+      <c r="H38" s="14">
+        <v>0</v>
+      </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
         <v>670</v>
@@ -1785,7 +1799,9 @@
       <c r="G39" s="14">
         <v>6</v>
       </c>
-      <c r="H39" s="14"/>
+      <c r="H39" s="14">
+        <v>0</v>
+      </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
         <v>785</v>
@@ -1864,14 +1880,18 @@
       <c r="D41" s="14">
         <v>200</v>
       </c>
-      <c r="E41" s="14"/>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
       <c r="F41" s="14">
         <v>300</v>
       </c>
       <c r="G41" s="14">
         <v>6</v>
       </c>
-      <c r="H41" s="14"/>
+      <c r="H41" s="14">
+        <v>0</v>
+      </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
         <v>780</v>
@@ -1894,48 +1914,96 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B42" s="14">
+        <v>300</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>145</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>200</v>
+      </c>
+      <c r="G42" s="14">
+        <v>4</v>
+      </c>
+      <c r="H42" s="14">
+        <v>120</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>795</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>645</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B43" s="14">
+        <v>150</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>80</v>
+      </c>
+      <c r="E43" s="14">
+        <v>25</v>
+      </c>
+      <c r="F43" s="14">
+        <v>150</v>
+      </c>
+      <c r="G43" s="14">
+        <v>5</v>
+      </c>
+      <c r="H43" s="14">
+        <v>200</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>605</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>835</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>

--- a/12613711.xlsx
+++ b/12613711.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65992337-025D-4ED3-8F55-C977DA4ED78E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95225D48-5E28-4F3A-9420-ED66822775F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,21 @@
   </si>
   <si>
     <t>Mostly Induction</t>
+  </si>
+  <si>
+    <t>Most theroy</t>
+  </si>
+  <si>
+    <t>Lab practice</t>
+  </si>
+  <si>
+    <t>Mostly Theory</t>
+  </si>
+  <si>
+    <t>Regular practice</t>
+  </si>
+  <si>
+    <t>Concept Practice</t>
   </si>
 </sst>
 </file>
@@ -1820,7 +1835,7 @@
         <v>50</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -1864,7 +1879,7 @@
         <v>61</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -2006,114 +2021,232 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B44" s="14">
+        <v>200</v>
+      </c>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>250</v>
+      </c>
+      <c r="G44" s="14">
+        <v>5</v>
+      </c>
+      <c r="H44" s="14">
+        <v>200</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>670</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B45" s="14">
+        <v>300</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>180</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>200</v>
+      </c>
+      <c r="G45" s="14">
+        <v>4</v>
+      </c>
+      <c r="H45" s="14">
+        <v>0</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B46" s="14">
+        <v>250</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>200</v>
+      </c>
+      <c r="E46" s="14">
+        <v>40</v>
+      </c>
+      <c r="F46" s="14">
+        <v>150</v>
+      </c>
+      <c r="G46" s="14">
+        <v>3</v>
+      </c>
+      <c r="H46" s="14">
+        <v>0</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B47" s="14">
+        <v>450</v>
+      </c>
+      <c r="C47" s="14">
+        <v>120</v>
+      </c>
+      <c r="D47" s="14">
+        <v>125</v>
+      </c>
+      <c r="E47" s="14">
+        <v>35</v>
+      </c>
+      <c r="F47" s="14">
+        <v>250</v>
+      </c>
+      <c r="G47" s="14">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14">
+        <v>0</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B48" s="14">
+        <v>300</v>
+      </c>
+      <c r="C48" s="14">
+        <v>100</v>
+      </c>
+      <c r="D48" s="14">
+        <v>0</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>100</v>
+      </c>
+      <c r="G48" s="14">
+        <v>2</v>
+      </c>
+      <c r="H48" s="14">
+        <v>0</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>940</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
